--- a/3. G_Documents/4. Tài liệu/VNSH03/XFORCE_EMS_BOM_CAMBOX_RK3562_LOT500_2905.xlsx
+++ b/3. G_Documents/4. Tài liệu/VNSH03/XFORCE_EMS_BOM_CAMBOX_RK3562_LOT500_2905.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TungNM\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\4. Tài liệu\VNSH03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC424427-E8D0-40B9-BA35-EF83B99DB34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0A5517-B5DC-4129-83C3-6FC3B8AA9D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{F4D1D976-2D04-4FF3-8989-010921DC315D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F4D1D976-2D04-4FF3-8989-010921DC315D}"/>
   </bookViews>
   <sheets>
     <sheet name="Board GX" sheetId="5" r:id="rId1"/>
@@ -3470,21 +3470,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3497,11 +3482,26 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3524,6 +3524,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3541,24 +3559,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5640,38 +5640,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="76"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
       <c r="AE1" s="30"/>
       <c r="AF1" s="30"/>
       <c r="AG1" s="30"/>
@@ -5680,48 +5680,48 @@
       <c r="AJ1" s="30"/>
     </row>
     <row r="2" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78" t="s">
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="73" t="s">
         <v>553</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="80"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
       <c r="I2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="78" t="s">
+      <c r="J2" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="77" t="s">
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="79" t="s">
         <v>190</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="78" t="s">
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="81" t="s">
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="V2" s="82"/>
-      <c r="W2" s="78" t="s">
+      <c r="V2" s="78"/>
+      <c r="W2" s="73" t="s">
         <v>554</v>
       </c>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="80"/>
+      <c r="X2" s="74"/>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="75"/>
       <c r="AA2" s="14"/>
       <c r="AB2" s="13"/>
       <c r="AC2" s="13"/>
@@ -5734,46 +5734,46 @@
       <c r="AJ2" s="13"/>
     </row>
     <row r="3" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="78" t="s">
+      <c r="B3" s="77"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="73" t="s">
         <v>553</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="80"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="75"/>
       <c r="I3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="78" t="s">
+      <c r="J3" s="73" t="s">
         <v>826</v>
       </c>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="77" t="s">
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="78" t="s">
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="81" t="s">
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="V3" s="82"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="80"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="74"/>
+      <c r="Y3" s="74"/>
+      <c r="Z3" s="75"/>
       <c r="AA3" s="14"/>
       <c r="AB3" s="13"/>
       <c r="AC3" s="13"/>
@@ -5786,18 +5786,18 @@
       <c r="AJ3" s="13"/>
     </row>
     <row r="4" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="78" t="s">
+      <c r="B4" s="77"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="73" t="s">
         <v>763</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="80"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="16" t="s">
         <v>192</v>
       </c>
@@ -5807,27 +5807,27 @@
       <c r="K4" s="85"/>
       <c r="L4" s="85"/>
       <c r="M4" s="86"/>
-      <c r="N4" s="77" t="s">
+      <c r="N4" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
       <c r="Q4" s="87">
         <v>46168</v>
       </c>
       <c r="R4" s="88"/>
       <c r="S4" s="88"/>
       <c r="T4" s="89"/>
-      <c r="U4" s="81" t="s">
+      <c r="U4" s="76" t="s">
         <v>193</v>
       </c>
-      <c r="V4" s="82"/>
-      <c r="W4" s="78" t="s">
+      <c r="V4" s="78"/>
+      <c r="W4" s="73" t="s">
         <v>727</v>
       </c>
-      <c r="X4" s="79"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="80"/>
+      <c r="X4" s="74"/>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="75"/>
       <c r="AA4" s="14"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
@@ -5918,14 +5918,14 @@
       <c r="AD5" s="12"/>
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
-      <c r="AG5" s="73" t="s">
+      <c r="AG5" s="80" t="s">
         <v>839</v>
       </c>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="74"/>
-      <c r="AJ5" s="75"/>
-    </row>
-    <row r="6" spans="1:36" s="10" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="AH5" s="81"/>
+      <c r="AI5" s="81"/>
+      <c r="AJ5" s="82"/>
+    </row>
+    <row r="6" spans="1:36" s="10" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -7384,13 +7384,6 @@
   </sheetData>
   <autoFilter ref="A6:AJ19" xr:uid="{D0290F07-F12A-4D44-881E-154805A970A1}"/>
   <mergeCells count="23">
-    <mergeCell ref="W4:Z4"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:V3"/>
     <mergeCell ref="AG5:AJ5"/>
     <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A2:C2"/>
@@ -7407,6 +7400,13 @@
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="Q4:T4"/>
     <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:Z4"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:V3"/>
   </mergeCells>
   <conditionalFormatting sqref="I7:I8 I17:I19">
     <cfRule type="duplicateValues" dxfId="28" priority="7"/>
@@ -7513,38 +7513,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="76"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
       <c r="AE1" s="30"/>
       <c r="AF1" s="30"/>
       <c r="AG1" s="30"/>
@@ -7553,46 +7553,46 @@
       <c r="AJ1" s="30"/>
     </row>
     <row r="2" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78" t="s">
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="73" t="s">
         <v>553</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="80"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
       <c r="I2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="77" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="79" t="s">
         <v>190</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="78" t="s">
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="81" t="s">
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="V2" s="82"/>
-      <c r="W2" s="78" t="s">
+      <c r="V2" s="78"/>
+      <c r="W2" s="73" t="s">
         <v>554</v>
       </c>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="80"/>
+      <c r="X2" s="74"/>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="75"/>
       <c r="AA2" s="14"/>
       <c r="AB2" s="13"/>
       <c r="AC2" s="13"/>
@@ -7605,46 +7605,46 @@
       <c r="AJ2" s="13"/>
     </row>
     <row r="3" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="78" t="s">
+      <c r="B3" s="77"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="73" t="s">
         <v>553</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="80"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="75"/>
       <c r="I3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="78" t="s">
+      <c r="J3" s="73" t="s">
         <v>826</v>
       </c>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="77" t="s">
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="78" t="s">
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="81" t="s">
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="V3" s="82"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="80"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="74"/>
+      <c r="Y3" s="74"/>
+      <c r="Z3" s="75"/>
       <c r="AA3" s="14"/>
       <c r="AB3" s="13"/>
       <c r="AC3" s="13"/>
@@ -7657,18 +7657,18 @@
       <c r="AJ3" s="13"/>
     </row>
     <row r="4" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="78" t="s">
+      <c r="B4" s="77"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="73" t="s">
         <v>764</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="80"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="16" t="s">
         <v>192</v>
       </c>
@@ -7678,27 +7678,27 @@
       <c r="K4" s="85"/>
       <c r="L4" s="85"/>
       <c r="M4" s="86"/>
-      <c r="N4" s="77" t="s">
+      <c r="N4" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
       <c r="Q4" s="87">
         <v>46168</v>
       </c>
       <c r="R4" s="88"/>
       <c r="S4" s="88"/>
       <c r="T4" s="89"/>
-      <c r="U4" s="81" t="s">
+      <c r="U4" s="76" t="s">
         <v>193</v>
       </c>
-      <c r="V4" s="82"/>
-      <c r="W4" s="78" t="s">
+      <c r="V4" s="78"/>
+      <c r="W4" s="73" t="s">
         <v>727</v>
       </c>
-      <c r="X4" s="79"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="80"/>
+      <c r="X4" s="74"/>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="75"/>
       <c r="AA4" s="14"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
@@ -7789,14 +7789,14 @@
       <c r="AD5" s="12"/>
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
-      <c r="AG5" s="73" t="s">
+      <c r="AG5" s="80" t="s">
         <v>839</v>
       </c>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="74"/>
-      <c r="AJ5" s="75"/>
-    </row>
-    <row r="6" spans="1:36" s="10" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="AH5" s="81"/>
+      <c r="AI5" s="81"/>
+      <c r="AJ5" s="82"/>
+    </row>
+    <row r="6" spans="1:36" s="10" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" s="46" customFormat="1" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="46" customFormat="1" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -8966,7 +8966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:36" s="46" customFormat="1" ht="153" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" s="46" customFormat="1" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9976,13 +9976,6 @@
   </sheetData>
   <autoFilter ref="A6:AJ27" xr:uid="{3BBD31AD-8055-43D7-8363-0A1CCA2276FB}"/>
   <mergeCells count="23">
-    <mergeCell ref="W4:Z4"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:V3"/>
     <mergeCell ref="AG5:AJ5"/>
     <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A2:C2"/>
@@ -9999,6 +9992,13 @@
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="Q4:T4"/>
     <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:Z4"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:V3"/>
   </mergeCells>
   <conditionalFormatting sqref="I9:I13">
     <cfRule type="duplicateValues" dxfId="16" priority="9"/>
@@ -10113,38 +10113,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="76"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
       <c r="AE1" s="30"/>
       <c r="AF1" s="30"/>
       <c r="AG1" s="30"/>
@@ -10153,48 +10153,48 @@
       <c r="AJ1" s="30"/>
     </row>
     <row r="2" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78" t="s">
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="73" t="s">
         <v>553</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="80"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
       <c r="I2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="78" t="s">
+      <c r="J2" s="73" t="s">
         <v>555</v>
       </c>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="77" t="s">
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="79" t="s">
         <v>190</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="78" t="s">
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="81" t="s">
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="V2" s="82"/>
-      <c r="W2" s="78" t="s">
+      <c r="V2" s="78"/>
+      <c r="W2" s="73" t="s">
         <v>554</v>
       </c>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="80"/>
+      <c r="X2" s="74"/>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="75"/>
       <c r="AA2" s="14"/>
       <c r="AB2" s="13"/>
       <c r="AC2" s="13"/>
@@ -10207,46 +10207,46 @@
       <c r="AJ2" s="13"/>
     </row>
     <row r="3" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="78" t="s">
+      <c r="B3" s="77"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="73" t="s">
         <v>553</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="80"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="75"/>
       <c r="I3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="78" t="s">
+      <c r="J3" s="73" t="s">
         <v>826</v>
       </c>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="77" t="s">
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="78" t="s">
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="81" t="s">
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="V3" s="82"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="80"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="74"/>
+      <c r="Y3" s="74"/>
+      <c r="Z3" s="75"/>
       <c r="AA3" s="14"/>
       <c r="AB3" s="13"/>
       <c r="AC3" s="13"/>
@@ -10259,18 +10259,18 @@
       <c r="AJ3" s="13"/>
     </row>
     <row r="4" spans="1:36" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="78" t="s">
+      <c r="B4" s="77"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="73" t="s">
         <v>552</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="80"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="16" t="s">
         <v>192</v>
       </c>
@@ -10280,25 +10280,25 @@
       <c r="K4" s="85"/>
       <c r="L4" s="85"/>
       <c r="M4" s="86"/>
-      <c r="N4" s="77" t="s">
+      <c r="N4" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
       <c r="Q4" s="87">
         <v>46168</v>
       </c>
       <c r="R4" s="88"/>
       <c r="S4" s="88"/>
       <c r="T4" s="89"/>
-      <c r="U4" s="81" t="s">
+      <c r="U4" s="76" t="s">
         <v>193</v>
       </c>
-      <c r="V4" s="82"/>
-      <c r="W4" s="78"/>
-      <c r="X4" s="79"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="80"/>
+      <c r="V4" s="78"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="74"/>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="75"/>
       <c r="AA4" s="14"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
@@ -10391,14 +10391,14 @@
       <c r="AD5" s="12"/>
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
-      <c r="AG5" s="73" t="s">
+      <c r="AG5" s="80" t="s">
         <v>839</v>
       </c>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="74"/>
-      <c r="AJ5" s="75"/>
-    </row>
-    <row r="6" spans="1:36" s="10" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="AH5" s="81"/>
+      <c r="AI5" s="81"/>
+      <c r="AJ5" s="82"/>
+    </row>
+    <row r="6" spans="1:36" s="10" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -25486,13 +25486,6 @@
   </sheetData>
   <autoFilter ref="A6:AJ149" xr:uid="{20E025CD-ADCA-48F2-AE95-3B3CDAFC39B2}"/>
   <mergeCells count="23">
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
     <mergeCell ref="AG5:AJ5"/>
     <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A2:C2"/>
@@ -25509,6 +25502,13 @@
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
@@ -26588,58 +26588,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="99" t="s">
         <v>849</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="95" t="s">
+      <c r="B1" s="99"/>
+      <c r="C1" s="101" t="s">
         <v>850</v>
       </c>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
     </row>
     <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="93"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="96" t="s">
+      <c r="A2" s="99"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="102" t="s">
         <v>851</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
     </row>
     <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="93"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="96" t="s">
+      <c r="A3" s="99"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="102" t="s">
         <v>852</v>
       </c>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
     </row>
     <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="94"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="96" t="s">
+      <c r="A4" s="100"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="102" t="s">
         <v>853</v>
       </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
     </row>
     <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="97" t="s">
         <v>854</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
     </row>
     <row r="6" spans="1:5" ht="2.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="98"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="100"/>
+      <c r="A6" s="92"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
     </row>
     <row r="7" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49" t="s">
@@ -26707,7 +26707,7 @@
       <c r="D12" s="59">
         <v>489</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="95" t="s">
         <v>865</v>
       </c>
     </row>
@@ -26724,7 +26724,7 @@
       <c r="D13" s="59">
         <v>488</v>
       </c>
-      <c r="E13" s="101"/>
+      <c r="E13" s="95"/>
     </row>
     <row r="14" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58">
@@ -26739,7 +26739,7 @@
       <c r="D14" s="59">
         <v>3465</v>
       </c>
-      <c r="E14" s="101"/>
+      <c r="E14" s="95"/>
     </row>
     <row r="15" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
@@ -26754,7 +26754,7 @@
       <c r="D15" s="59">
         <v>990</v>
       </c>
-      <c r="E15" s="101"/>
+      <c r="E15" s="95"/>
     </row>
     <row r="16" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="58">
@@ -26769,7 +26769,7 @@
       <c r="D16" s="59">
         <v>990</v>
       </c>
-      <c r="E16" s="101"/>
+      <c r="E16" s="95"/>
     </row>
     <row r="17" spans="1:5" s="57" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58">
@@ -26784,7 +26784,7 @@
       <c r="D17" s="59">
         <v>2475</v>
       </c>
-      <c r="E17" s="101"/>
+      <c r="E17" s="95"/>
     </row>
     <row r="18" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58">
@@ -26799,7 +26799,7 @@
       <c r="D18" s="59">
         <v>5445</v>
       </c>
-      <c r="E18" s="101"/>
+      <c r="E18" s="95"/>
     </row>
     <row r="19" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
@@ -26814,7 +26814,7 @@
       <c r="D19" s="59">
         <v>990</v>
       </c>
-      <c r="E19" s="101"/>
+      <c r="E19" s="95"/>
     </row>
     <row r="20" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
@@ -26829,7 +26829,7 @@
       <c r="D20" s="59">
         <v>495</v>
       </c>
-      <c r="E20" s="101"/>
+      <c r="E20" s="95"/>
     </row>
     <row r="21" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58">
@@ -26844,7 +26844,7 @@
       <c r="D21" s="59">
         <v>40570</v>
       </c>
-      <c r="E21" s="101"/>
+      <c r="E21" s="95"/>
     </row>
     <row r="22" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58">
@@ -26859,7 +26859,7 @@
       <c r="D22" s="59">
         <v>990</v>
       </c>
-      <c r="E22" s="101"/>
+      <c r="E22" s="95"/>
     </row>
     <row r="23" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58">
@@ -26874,7 +26874,7 @@
       <c r="D23" s="59">
         <v>495</v>
       </c>
-      <c r="E23" s="101"/>
+      <c r="E23" s="95"/>
     </row>
     <row r="24" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
@@ -26889,7 +26889,7 @@
       <c r="D24" s="59">
         <v>495</v>
       </c>
-      <c r="E24" s="101"/>
+      <c r="E24" s="95"/>
     </row>
     <row r="25" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58">
@@ -26904,7 +26904,7 @@
       <c r="D25" s="59">
         <v>495</v>
       </c>
-      <c r="E25" s="101"/>
+      <c r="E25" s="95"/>
     </row>
     <row r="26" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58">
@@ -26919,7 +26919,7 @@
       <c r="D26" s="59">
         <v>495</v>
       </c>
-      <c r="E26" s="101"/>
+      <c r="E26" s="95"/>
     </row>
     <row r="27" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58">
@@ -26934,7 +26934,7 @@
       <c r="D27" s="59">
         <v>495</v>
       </c>
-      <c r="E27" s="101"/>
+      <c r="E27" s="95"/>
     </row>
     <row r="28" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="58">
@@ -26949,7 +26949,7 @@
       <c r="D28" s="59">
         <v>495</v>
       </c>
-      <c r="E28" s="101"/>
+      <c r="E28" s="95"/>
     </row>
     <row r="29" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58">
@@ -26964,7 +26964,7 @@
       <c r="D29" s="59">
         <v>3945</v>
       </c>
-      <c r="E29" s="101"/>
+      <c r="E29" s="95"/>
     </row>
     <row r="30" spans="1:5" s="57" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="58">
@@ -26979,7 +26979,7 @@
       <c r="D30" s="59">
         <v>13360</v>
       </c>
-      <c r="E30" s="101"/>
+      <c r="E30" s="95"/>
     </row>
     <row r="31" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58">
@@ -26994,7 +26994,7 @@
       <c r="D31" s="59">
         <v>1485</v>
       </c>
-      <c r="E31" s="101"/>
+      <c r="E31" s="95"/>
     </row>
     <row r="32" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="58">
@@ -27009,7 +27009,7 @@
       <c r="D32" s="59">
         <v>3960</v>
       </c>
-      <c r="E32" s="101"/>
+      <c r="E32" s="95"/>
     </row>
     <row r="33" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
@@ -27024,7 +27024,7 @@
       <c r="D33" s="59">
         <v>495</v>
       </c>
-      <c r="E33" s="101"/>
+      <c r="E33" s="95"/>
     </row>
     <row r="34" spans="1:5" s="57" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="58">
@@ -27039,7 +27039,7 @@
       <c r="D34" s="59">
         <v>495</v>
       </c>
-      <c r="E34" s="101"/>
+      <c r="E34" s="95"/>
     </row>
     <row r="35" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
@@ -27054,7 +27054,7 @@
       <c r="D35" s="59">
         <v>990</v>
       </c>
-      <c r="E35" s="101"/>
+      <c r="E35" s="95"/>
     </row>
     <row r="36" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
@@ -27069,7 +27069,7 @@
       <c r="D36" s="59">
         <v>495</v>
       </c>
-      <c r="E36" s="101"/>
+      <c r="E36" s="95"/>
     </row>
     <row r="37" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58">
@@ -27084,7 +27084,7 @@
       <c r="D37" s="59">
         <v>495</v>
       </c>
-      <c r="E37" s="101"/>
+      <c r="E37" s="95"/>
     </row>
     <row r="38" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
@@ -27099,7 +27099,7 @@
       <c r="D38" s="59">
         <v>495</v>
       </c>
-      <c r="E38" s="101"/>
+      <c r="E38" s="95"/>
     </row>
     <row r="39" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
@@ -27114,7 +27114,7 @@
       <c r="D39" s="59">
         <v>990</v>
       </c>
-      <c r="E39" s="101"/>
+      <c r="E39" s="95"/>
     </row>
     <row r="40" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58">
@@ -27129,7 +27129,7 @@
       <c r="D40" s="59">
         <v>990</v>
       </c>
-      <c r="E40" s="101"/>
+      <c r="E40" s="95"/>
     </row>
     <row r="41" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58">
@@ -27144,7 +27144,7 @@
       <c r="D41" s="59">
         <v>495</v>
       </c>
-      <c r="E41" s="101"/>
+      <c r="E41" s="95"/>
     </row>
     <row r="42" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="58">
@@ -27159,7 +27159,7 @@
       <c r="D42" s="59">
         <v>495</v>
       </c>
-      <c r="E42" s="101"/>
+      <c r="E42" s="95"/>
     </row>
     <row r="43" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
@@ -27174,7 +27174,7 @@
       <c r="D43" s="59">
         <v>495</v>
       </c>
-      <c r="E43" s="101"/>
+      <c r="E43" s="95"/>
     </row>
     <row r="44" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="58">
@@ -27189,7 +27189,7 @@
       <c r="D44" s="59">
         <v>985</v>
       </c>
-      <c r="E44" s="101"/>
+      <c r="E44" s="95"/>
     </row>
     <row r="45" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="58">
@@ -27204,7 +27204,7 @@
       <c r="D45" s="59">
         <v>495</v>
       </c>
-      <c r="E45" s="101"/>
+      <c r="E45" s="95"/>
     </row>
     <row r="46" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="58">
@@ -27219,7 +27219,7 @@
       <c r="D46" s="59">
         <v>495</v>
       </c>
-      <c r="E46" s="101"/>
+      <c r="E46" s="95"/>
     </row>
     <row r="47" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="58">
@@ -27234,7 +27234,7 @@
       <c r="D47" s="59">
         <v>500</v>
       </c>
-      <c r="E47" s="101"/>
+      <c r="E47" s="95"/>
     </row>
     <row r="48" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="58">
@@ -27249,7 +27249,7 @@
       <c r="D48" s="59">
         <v>495</v>
       </c>
-      <c r="E48" s="101"/>
+      <c r="E48" s="95"/>
     </row>
     <row r="49" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="58">
@@ -27264,7 +27264,7 @@
       <c r="D49" s="59">
         <v>495</v>
       </c>
-      <c r="E49" s="101"/>
+      <c r="E49" s="95"/>
     </row>
     <row r="50" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="58">
@@ -27279,7 +27279,7 @@
       <c r="D50" s="59">
         <v>4445</v>
       </c>
-      <c r="E50" s="101"/>
+      <c r="E50" s="95"/>
     </row>
     <row r="51" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58">
@@ -27294,7 +27294,7 @@
       <c r="D51" s="59">
         <v>2970</v>
       </c>
-      <c r="E51" s="101"/>
+      <c r="E51" s="95"/>
     </row>
     <row r="52" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="58">
@@ -27309,7 +27309,7 @@
       <c r="D52" s="59">
         <v>495</v>
       </c>
-      <c r="E52" s="101"/>
+      <c r="E52" s="95"/>
     </row>
     <row r="53" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="58">
@@ -27324,7 +27324,7 @@
       <c r="D53" s="59">
         <v>495</v>
       </c>
-      <c r="E53" s="101"/>
+      <c r="E53" s="95"/>
     </row>
     <row r="54" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="58">
@@ -27339,7 +27339,7 @@
       <c r="D54" s="59">
         <v>490</v>
       </c>
-      <c r="E54" s="101"/>
+      <c r="E54" s="95"/>
     </row>
     <row r="55" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="58">
@@ -27354,7 +27354,7 @@
       <c r="D55" s="59">
         <v>6915</v>
       </c>
-      <c r="E55" s="101"/>
+      <c r="E55" s="95"/>
     </row>
     <row r="56" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="58">
@@ -27369,7 +27369,7 @@
       <c r="D56" s="59">
         <v>495</v>
       </c>
-      <c r="E56" s="101"/>
+      <c r="E56" s="95"/>
     </row>
     <row r="57" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="58">
@@ -27384,7 +27384,7 @@
       <c r="D57" s="59">
         <v>2475</v>
       </c>
-      <c r="E57" s="101"/>
+      <c r="E57" s="95"/>
     </row>
     <row r="58" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="58">
@@ -27399,7 +27399,7 @@
       <c r="D58" s="59">
         <v>990</v>
       </c>
-      <c r="E58" s="101"/>
+      <c r="E58" s="95"/>
     </row>
     <row r="59" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="58">
@@ -27414,7 +27414,7 @@
       <c r="D59" s="59">
         <v>495</v>
       </c>
-      <c r="E59" s="101"/>
+      <c r="E59" s="95"/>
     </row>
     <row r="60" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58">
@@ -27429,7 +27429,7 @@
       <c r="D60" s="59">
         <v>495</v>
       </c>
-      <c r="E60" s="101"/>
+      <c r="E60" s="95"/>
     </row>
     <row r="61" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="58">
@@ -27444,7 +27444,7 @@
       <c r="D61" s="59">
         <v>990</v>
       </c>
-      <c r="E61" s="101"/>
+      <c r="E61" s="95"/>
     </row>
     <row r="62" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58">
@@ -27459,7 +27459,7 @@
       <c r="D62" s="59">
         <v>4950</v>
       </c>
-      <c r="E62" s="101"/>
+      <c r="E62" s="95"/>
     </row>
     <row r="63" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="58">
@@ -27474,7 +27474,7 @@
       <c r="D63" s="59">
         <v>2970</v>
       </c>
-      <c r="E63" s="101"/>
+      <c r="E63" s="95"/>
     </row>
     <row r="64" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58">
@@ -27489,7 +27489,7 @@
       <c r="D64" s="59">
         <v>6435</v>
       </c>
-      <c r="E64" s="101"/>
+      <c r="E64" s="95"/>
     </row>
     <row r="65" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="58">
@@ -27504,7 +27504,7 @@
       <c r="D65" s="59">
         <v>990</v>
       </c>
-      <c r="E65" s="101"/>
+      <c r="E65" s="95"/>
     </row>
     <row r="66" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="58" t="s">
@@ -27519,7 +27519,7 @@
       <c r="D66" s="59">
         <v>495</v>
       </c>
-      <c r="E66" s="101"/>
+      <c r="E66" s="95"/>
     </row>
     <row r="67" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="58">
@@ -27534,7 +27534,7 @@
       <c r="D67" s="59">
         <v>990</v>
       </c>
-      <c r="E67" s="101"/>
+      <c r="E67" s="95"/>
     </row>
     <row r="68" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58">
@@ -27549,7 +27549,7 @@
       <c r="D68" s="59">
         <v>495</v>
       </c>
-      <c r="E68" s="101"/>
+      <c r="E68" s="95"/>
     </row>
     <row r="69" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="58">
@@ -27564,7 +27564,7 @@
       <c r="D69" s="59">
         <v>495</v>
       </c>
-      <c r="E69" s="101"/>
+      <c r="E69" s="95"/>
     </row>
     <row r="70" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58">
@@ -27579,7 +27579,7 @@
       <c r="D70" s="59">
         <v>1980</v>
       </c>
-      <c r="E70" s="101"/>
+      <c r="E70" s="95"/>
     </row>
     <row r="71" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="58">
@@ -27594,7 +27594,7 @@
       <c r="D71" s="59">
         <v>1485</v>
       </c>
-      <c r="E71" s="101"/>
+      <c r="E71" s="95"/>
     </row>
     <row r="72" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="58">
@@ -27609,7 +27609,7 @@
       <c r="D72" s="59">
         <v>990</v>
       </c>
-      <c r="E72" s="101"/>
+      <c r="E72" s="95"/>
     </row>
     <row r="73" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="58">
@@ -27624,7 +27624,7 @@
       <c r="D73" s="59">
         <v>495</v>
       </c>
-      <c r="E73" s="101"/>
+      <c r="E73" s="95"/>
     </row>
     <row r="74" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58">
@@ -27639,7 +27639,7 @@
       <c r="D74" s="59">
         <v>495</v>
       </c>
-      <c r="E74" s="101"/>
+      <c r="E74" s="95"/>
     </row>
     <row r="75" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="58">
@@ -27654,7 +27654,7 @@
       <c r="D75" s="59">
         <v>495</v>
       </c>
-      <c r="E75" s="101"/>
+      <c r="E75" s="95"/>
     </row>
     <row r="76" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="58">
@@ -27669,7 +27669,7 @@
       <c r="D76" s="59">
         <v>495</v>
       </c>
-      <c r="E76" s="101"/>
+      <c r="E76" s="95"/>
     </row>
     <row r="77" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="58">
@@ -27684,7 +27684,7 @@
       <c r="D77" s="59">
         <v>495</v>
       </c>
-      <c r="E77" s="101"/>
+      <c r="E77" s="95"/>
     </row>
     <row r="78" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="58">
@@ -27699,7 +27699,7 @@
       <c r="D78" s="59">
         <v>495</v>
       </c>
-      <c r="E78" s="101"/>
+      <c r="E78" s="95"/>
     </row>
     <row r="79" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="58">
@@ -27714,7 +27714,7 @@
       <c r="D79" s="59">
         <v>495</v>
       </c>
-      <c r="E79" s="101"/>
+      <c r="E79" s="95"/>
     </row>
     <row r="80" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="58">
@@ -27729,7 +27729,7 @@
       <c r="D80" s="59">
         <v>495</v>
       </c>
-      <c r="E80" s="101"/>
+      <c r="E80" s="95"/>
     </row>
     <row r="81" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="58">
@@ -27744,7 +27744,7 @@
       <c r="D81" s="59">
         <v>990</v>
       </c>
-      <c r="E81" s="101"/>
+      <c r="E81" s="95"/>
     </row>
     <row r="82" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="58">
@@ -27759,7 +27759,7 @@
       <c r="D82" s="59">
         <v>495</v>
       </c>
-      <c r="E82" s="101"/>
+      <c r="E82" s="95"/>
     </row>
     <row r="83" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="58">
@@ -27774,7 +27774,7 @@
       <c r="D83" s="59">
         <v>495</v>
       </c>
-      <c r="E83" s="101"/>
+      <c r="E83" s="95"/>
     </row>
     <row r="84" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="58">
@@ -27789,7 +27789,7 @@
       <c r="D84" s="59">
         <v>1480</v>
       </c>
-      <c r="E84" s="101"/>
+      <c r="E84" s="95"/>
     </row>
     <row r="85" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="58">
@@ -27804,7 +27804,7 @@
       <c r="D85" s="59">
         <v>1485</v>
       </c>
-      <c r="E85" s="101"/>
+      <c r="E85" s="95"/>
     </row>
     <row r="86" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="58">
@@ -27819,7 +27819,7 @@
       <c r="D86" s="59">
         <v>495</v>
       </c>
-      <c r="E86" s="101"/>
+      <c r="E86" s="95"/>
     </row>
     <row r="87" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="58">
@@ -27834,7 +27834,7 @@
       <c r="D87" s="59">
         <v>3455</v>
       </c>
-      <c r="E87" s="101"/>
+      <c r="E87" s="95"/>
     </row>
     <row r="88" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="58">
@@ -27849,7 +27849,7 @@
       <c r="D88" s="59">
         <v>495</v>
       </c>
-      <c r="E88" s="101"/>
+      <c r="E88" s="95"/>
     </row>
     <row r="89" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="58">
@@ -27864,7 +27864,7 @@
       <c r="D89" s="59">
         <v>2970</v>
       </c>
-      <c r="E89" s="101"/>
+      <c r="E89" s="95"/>
     </row>
     <row r="90" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="58">
@@ -27879,7 +27879,7 @@
       <c r="D90" s="59">
         <v>495</v>
       </c>
-      <c r="E90" s="101"/>
+      <c r="E90" s="95"/>
     </row>
     <row r="91" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="58">
@@ -27894,7 +27894,7 @@
       <c r="D91" s="59">
         <v>495</v>
       </c>
-      <c r="E91" s="101"/>
+      <c r="E91" s="95"/>
     </row>
     <row r="92" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="58">
@@ -27909,7 +27909,7 @@
       <c r="D92" s="59">
         <v>4950</v>
       </c>
-      <c r="E92" s="101"/>
+      <c r="E92" s="95"/>
     </row>
     <row r="93" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="58">
@@ -27924,7 +27924,7 @@
       <c r="D93" s="59">
         <v>495</v>
       </c>
-      <c r="E93" s="101"/>
+      <c r="E93" s="95"/>
     </row>
     <row r="94" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="58">
@@ -27939,7 +27939,7 @@
       <c r="D94" s="59">
         <v>21090</v>
       </c>
-      <c r="E94" s="101"/>
+      <c r="E94" s="95"/>
     </row>
     <row r="95" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="58">
@@ -27954,7 +27954,7 @@
       <c r="D95" s="59">
         <v>16805</v>
       </c>
-      <c r="E95" s="101"/>
+      <c r="E95" s="95"/>
     </row>
     <row r="96" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="58">
@@ -27969,7 +27969,7 @@
       <c r="D96" s="59">
         <v>495</v>
       </c>
-      <c r="E96" s="101"/>
+      <c r="E96" s="95"/>
     </row>
     <row r="97" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="58">
@@ -27984,7 +27984,7 @@
       <c r="D97" s="59">
         <v>495</v>
       </c>
-      <c r="E97" s="101"/>
+      <c r="E97" s="95"/>
     </row>
     <row r="98" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="58">
@@ -27999,7 +27999,7 @@
       <c r="D98" s="59">
         <v>990</v>
       </c>
-      <c r="E98" s="101"/>
+      <c r="E98" s="95"/>
     </row>
     <row r="99" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="58">
@@ -28014,7 +28014,7 @@
       <c r="D99" s="59">
         <v>495</v>
       </c>
-      <c r="E99" s="101"/>
+      <c r="E99" s="95"/>
     </row>
     <row r="100" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="58">
@@ -28029,7 +28029,7 @@
       <c r="D100" s="59">
         <v>500</v>
       </c>
-      <c r="E100" s="101"/>
+      <c r="E100" s="95"/>
     </row>
     <row r="101" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="58">
@@ -28044,7 +28044,7 @@
       <c r="D101" s="59">
         <v>495</v>
       </c>
-      <c r="E101" s="101"/>
+      <c r="E101" s="95"/>
     </row>
     <row r="102" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="58">
@@ -28059,7 +28059,7 @@
       <c r="D102" s="59">
         <v>2475</v>
       </c>
-      <c r="E102" s="101"/>
+      <c r="E102" s="95"/>
     </row>
     <row r="103" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="58">
@@ -28074,7 +28074,7 @@
       <c r="D103" s="59">
         <v>9385</v>
       </c>
-      <c r="E103" s="101"/>
+      <c r="E103" s="95"/>
     </row>
     <row r="104" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="58">
@@ -28089,7 +28089,7 @@
       <c r="D104" s="59">
         <v>495</v>
       </c>
-      <c r="E104" s="101"/>
+      <c r="E104" s="95"/>
     </row>
     <row r="105" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="58">
@@ -28104,7 +28104,7 @@
       <c r="D105" s="59">
         <v>495</v>
       </c>
-      <c r="E105" s="101"/>
+      <c r="E105" s="95"/>
     </row>
     <row r="106" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="58">
@@ -28119,7 +28119,7 @@
       <c r="D106" s="59">
         <v>495</v>
       </c>
-      <c r="E106" s="101"/>
+      <c r="E106" s="95"/>
     </row>
     <row r="107" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="58">
@@ -28134,7 +28134,7 @@
       <c r="D107" s="59">
         <v>495</v>
       </c>
-      <c r="E107" s="101"/>
+      <c r="E107" s="95"/>
     </row>
     <row r="108" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="58">
@@ -28149,7 +28149,7 @@
       <c r="D108" s="59">
         <v>7400</v>
       </c>
-      <c r="E108" s="101"/>
+      <c r="E108" s="95"/>
     </row>
     <row r="109" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="58">
@@ -28164,7 +28164,7 @@
       <c r="D109" s="59">
         <v>990</v>
       </c>
-      <c r="E109" s="101"/>
+      <c r="E109" s="95"/>
     </row>
     <row r="110" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="58">
@@ -28179,7 +28179,7 @@
       <c r="D110" s="59">
         <v>13365</v>
       </c>
-      <c r="E110" s="101"/>
+      <c r="E110" s="95"/>
     </row>
     <row r="111" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="58">
@@ -28194,7 +28194,7 @@
       <c r="D111" s="59">
         <v>495</v>
       </c>
-      <c r="E111" s="101"/>
+      <c r="E111" s="95"/>
     </row>
     <row r="112" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="58">
@@ -28209,7 +28209,7 @@
       <c r="D112" s="59">
         <v>990</v>
       </c>
-      <c r="E112" s="101"/>
+      <c r="E112" s="95"/>
     </row>
     <row r="113" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="58">
@@ -28224,7 +28224,7 @@
       <c r="D113" s="59">
         <v>10000</v>
       </c>
-      <c r="E113" s="101"/>
+      <c r="E113" s="95"/>
     </row>
     <row r="114" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="58">
@@ -28239,7 +28239,7 @@
       <c r="D114" s="59">
         <v>490</v>
       </c>
-      <c r="E114" s="101"/>
+      <c r="E114" s="95"/>
     </row>
     <row r="115" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="58">
@@ -28254,7 +28254,7 @@
       <c r="D115" s="59">
         <v>495</v>
       </c>
-      <c r="E115" s="101"/>
+      <c r="E115" s="95"/>
     </row>
     <row r="116" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="58">
@@ -28269,7 +28269,7 @@
       <c r="D116" s="59">
         <v>4450</v>
       </c>
-      <c r="E116" s="101"/>
+      <c r="E116" s="95"/>
     </row>
     <row r="117" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="58">
@@ -28284,7 +28284,7 @@
       <c r="D117" s="59">
         <v>1980</v>
       </c>
-      <c r="E117" s="101"/>
+      <c r="E117" s="95"/>
     </row>
     <row r="118" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="58">
@@ -28299,7 +28299,7 @@
       <c r="D118" s="59">
         <v>495</v>
       </c>
-      <c r="E118" s="101"/>
+      <c r="E118" s="95"/>
     </row>
     <row r="119" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="58">
@@ -28314,7 +28314,7 @@
       <c r="D119" s="59">
         <v>8420</v>
       </c>
-      <c r="E119" s="101"/>
+      <c r="E119" s="95"/>
     </row>
     <row r="120" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="58">
@@ -28329,7 +28329,7 @@
       <c r="D120" s="59">
         <v>495</v>
       </c>
-      <c r="E120" s="101"/>
+      <c r="E120" s="95"/>
     </row>
     <row r="121" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="58">
@@ -28344,7 +28344,7 @@
       <c r="D121" s="59">
         <v>495</v>
       </c>
-      <c r="E121" s="101"/>
+      <c r="E121" s="95"/>
     </row>
     <row r="122" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="58">
@@ -28359,7 +28359,7 @@
       <c r="D122" s="59">
         <v>495</v>
       </c>
-      <c r="E122" s="101"/>
+      <c r="E122" s="95"/>
     </row>
     <row r="123" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
@@ -28374,7 +28374,7 @@
       <c r="D123" s="59">
         <v>495</v>
       </c>
-      <c r="E123" s="101"/>
+      <c r="E123" s="95"/>
     </row>
     <row r="124" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="58">
@@ -28389,7 +28389,7 @@
       <c r="D124" s="59">
         <v>495</v>
       </c>
-      <c r="E124" s="101"/>
+      <c r="E124" s="95"/>
     </row>
     <row r="125" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="58">
@@ -28404,7 +28404,7 @@
       <c r="D125" s="59">
         <v>495</v>
       </c>
-      <c r="E125" s="101"/>
+      <c r="E125" s="95"/>
     </row>
     <row r="126" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="58">
@@ -28419,7 +28419,7 @@
       <c r="D126" s="59">
         <v>495</v>
       </c>
-      <c r="E126" s="101"/>
+      <c r="E126" s="95"/>
     </row>
     <row r="127" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="58">
@@ -28434,7 +28434,7 @@
       <c r="D127" s="59">
         <v>495</v>
       </c>
-      <c r="E127" s="101"/>
+      <c r="E127" s="95"/>
     </row>
     <row r="128" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="58">
@@ -28449,7 +28449,7 @@
       <c r="D128" s="59">
         <v>495</v>
       </c>
-      <c r="E128" s="101"/>
+      <c r="E128" s="95"/>
     </row>
     <row r="129" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="58">
@@ -28464,7 +28464,7 @@
       <c r="D129" s="59">
         <v>1325</v>
       </c>
-      <c r="E129" s="101"/>
+      <c r="E129" s="95"/>
     </row>
     <row r="130" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="58">
@@ -28479,7 +28479,7 @@
       <c r="D130" s="59">
         <v>495</v>
       </c>
-      <c r="E130" s="101"/>
+      <c r="E130" s="95"/>
     </row>
     <row r="131" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="58">
@@ -28494,7 +28494,7 @@
       <c r="D131" s="59">
         <v>495</v>
       </c>
-      <c r="E131" s="101"/>
+      <c r="E131" s="95"/>
     </row>
     <row r="132" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="58">
@@ -28509,7 +28509,7 @@
       <c r="D132" s="59">
         <v>11380</v>
       </c>
-      <c r="E132" s="101"/>
+      <c r="E132" s="95"/>
     </row>
     <row r="133" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="58">
@@ -28524,7 +28524,7 @@
       <c r="D133" s="59">
         <v>495</v>
       </c>
-      <c r="E133" s="101"/>
+      <c r="E133" s="95"/>
     </row>
     <row r="134" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="58">
@@ -28539,7 +28539,7 @@
       <c r="D134" s="59">
         <v>495</v>
       </c>
-      <c r="E134" s="101"/>
+      <c r="E134" s="95"/>
     </row>
     <row r="135" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="58">
@@ -28554,7 +28554,7 @@
       <c r="D135" s="59">
         <v>1485</v>
       </c>
-      <c r="E135" s="101"/>
+      <c r="E135" s="95"/>
     </row>
     <row r="136" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="58">
@@ -28569,7 +28569,7 @@
       <c r="D136" s="59">
         <v>495</v>
       </c>
-      <c r="E136" s="101"/>
+      <c r="E136" s="95"/>
     </row>
     <row r="137" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="58">
@@ -28584,7 +28584,7 @@
       <c r="D137" s="59">
         <v>990</v>
       </c>
-      <c r="E137" s="101"/>
+      <c r="E137" s="95"/>
     </row>
     <row r="138" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="58">
@@ -28599,7 +28599,7 @@
       <c r="D138" s="59">
         <v>495</v>
       </c>
-      <c r="E138" s="101"/>
+      <c r="E138" s="95"/>
     </row>
     <row r="139" spans="1:5" s="57" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="58">
@@ -28716,26 +28716,26 @@
       <c r="E146" s="62"/>
     </row>
     <row r="147" spans="1:5" s="57" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="97" t="s">
+      <c r="A147" s="91" t="s">
         <v>874</v>
       </c>
-      <c r="B147" s="97"/>
+      <c r="B147" s="91"/>
       <c r="C147" s="60"/>
-      <c r="D147" s="97" t="s">
+      <c r="D147" s="91" t="s">
         <v>875</v>
       </c>
-      <c r="E147" s="97"/>
+      <c r="E147" s="91"/>
     </row>
     <row r="148" spans="1:5" s="57" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="102" t="s">
+      <c r="A148" s="96" t="s">
         <v>876</v>
       </c>
-      <c r="B148" s="102"/>
+      <c r="B148" s="96"/>
       <c r="C148" s="63"/>
-      <c r="D148" s="102" t="s">
+      <c r="D148" s="96" t="s">
         <v>876</v>
       </c>
-      <c r="E148" s="102"/>
+      <c r="E148" s="96"/>
     </row>
     <row r="149" spans="1:5" s="57" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="60"/>
@@ -28773,11 +28773,11 @@
       <c r="E153" s="60"/>
     </row>
     <row r="154" spans="1:5" s="57" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="97"/>
-      <c r="B154" s="97"/>
+      <c r="A154" s="91"/>
+      <c r="B154" s="91"/>
       <c r="C154" s="60"/>
-      <c r="D154" s="97"/>
-      <c r="E154" s="97"/>
+      <c r="D154" s="91"/>
+      <c r="E154" s="91"/>
     </row>
     <row r="155" spans="1:5" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="156" spans="1:5" s="57" customFormat="1" x14ac:dyDescent="0.25">
@@ -28806,6 +28806,12 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="14">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="A154:B154"/>
     <mergeCell ref="D154:E154"/>
     <mergeCell ref="A6:E6"/>
@@ -28814,12 +28820,6 @@
     <mergeCell ref="D147:E147"/>
     <mergeCell ref="A148:B148"/>
     <mergeCell ref="D148:E148"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
